--- a/docs/almica-contenido-v2-20260924-1451-fix.xlsx
+++ b/docs/almica-contenido-v2-20260924-1451-fix.xlsx
@@ -718,6 +718,21 @@
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
+    <author>Pendientes</author>
+  </authors>
+  <commentList>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>La marca no usa TikTok (confirmado). Se dejó vacío y el icono está comentado en el tema. Si abren cuenta, pega aquí la URL y descomenta social_tiktok en template-parts/footer/social.php.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
     <author>None</author>
   </authors>
   <commentList>
@@ -743,7 +758,7 @@
 </comments>
 </file>
 
-<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={cdb6e703-4719-4979-8d8d-705291c79772}</author>
@@ -12032,7 +12047,7 @@
       </c>
       <c r="F3" s="36" t="inlineStr">
         <is>
-          <t>Un programa enfocado en el desarrollo del autoconocimiento profundo y la conexión con el propósito personal.</t>
+          <t>Un viaje de profundización en la percepción energética y el lenguaje sutil del cuerpo.</t>
         </is>
       </c>
       <c r="G3" s="36" t="inlineStr">
@@ -12095,7 +12110,7 @@
       </c>
       <c r="F4" s="36" t="inlineStr">
         <is>
-          <t>Un espacio de formación enfocado en el desarrollo de la conciencia y la conexión con dimensiones más profundas del ser.</t>
+          <t>Herramientas para acceder a estados expandidos de consciencia y trabajar desde ahí.</t>
         </is>
       </c>
       <c r="G4" s="36" t="inlineStr">
@@ -15824,7 +15839,11 @@
           <t>social_facebook</t>
         </is>
       </c>
-      <c r="B8" s="36" t="n"/>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100063472513452</t>
+        </is>
+      </c>
       <c r="C8" s="41" t="inlineStr">
         <is>
           <t>URL completa. Vacío oculta el botón.</t>
@@ -16966,5 +16985,6 @@
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/docs/almica-contenido-v2-20260924-1451-fix.xlsx
+++ b/docs/almica-contenido-v2-20260924-1451-fix.xlsx
@@ -5644,7 +5644,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>acerca-de-fundadora.jpg</t>
+          <t>alma-solis.jpg</t>
         </is>
       </c>
       <c r="F3" s="29" t="n">
@@ -5675,7 +5675,7 @@
       </c>
       <c r="E4" s="21" t="inlineStr">
         <is>
-          <t>elizabeth-de-las-casas.png</t>
+          <t>elizabeth-de-las-casas.jpg</t>
         </is>
       </c>
       <c r="F4" s="29" t="n">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>gabriela-dominguez.png</t>
+          <t>gabriela-dominguez.jpg</t>
         </is>
       </c>
       <c r="F5" s="29" t="n">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>tonathiu-munoz.png</t>
+          <t>tonathiu-munoz.jpg</t>
         </is>
       </c>
       <c r="F6" s="29" t="n">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E7" s="28" t="inlineStr">
         <is>
-          <t>perla-barrones.png</t>
+          <t>perla-barrones.jpg</t>
         </is>
       </c>
       <c r="F7" s="29" t="n">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="E8" s="30" t="inlineStr">
         <is>
-          <t>alberto-solis.png</t>
+          <t>alberto-solis.jpg</t>
         </is>
       </c>
       <c r="F8" s="26" t="n">

--- a/docs/almica-contenido-v2-20260924-1451-fix.xlsx
+++ b/docs/almica-contenido-v2-20260924-1451-fix.xlsx
@@ -988,7 +988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E47"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="3" customWidth="1" style="50" min="1" max="1"/>
@@ -998,6 +998,7 @@
     <col width="8.710000000000001" customWidth="1" style="50" min="6" max="26"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1019,6 +1020,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="7" t="inlineStr">
         <is>
@@ -1061,6 +1063,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="7" t="inlineStr">
         <is>
@@ -1104,6 +1107,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="30" customHeight="1" s="50">
       <c r="C18" s="15" t="inlineStr">
         <is>
@@ -1111,6 +1115,7 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -1174,7 +1179,7 @@
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Separa los slugs con una barra vertical, sin espacios: gabriela-dominguez|tonathiu-munoz</t>
+          <t>Separa los slugs con una barra vertical, sin espacios: gabriela-dominguez|tonatiuh-munoz</t>
         </is>
       </c>
     </row>
@@ -1225,14 +1230,14 @@
     <row r="31" ht="43.5" customHeight="1" s="50">
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Con tu hoja quedaron cubiertos 4 de los 11 servicios, los 3 cursos, Gabriela Domínguez y todos los textos de página. Lo urgente ahora son los 7 servicios que siguen sin página: hace falta descripción y beneficios en los 7, y el resumen corto en 5 de ellos. Después, el rol y la biografía de Tonathiu Muñoz, que imparte cinco de esos siete.</t>
+          <t>Con tu hoja quedaron cubiertos 4 de los 11 servicios, los 3 cursos, Gabriela Domínguez y todos los textos de página. Lo urgente ahora son los 7 servicios que siguen sin página: hace falta descripción y beneficios en los 7, y el resumen corto en 5 de ellos. Después, el rol y la biografía de Tonatiuh Muñoz, que imparte cinco de esos siete.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="43.5" customHeight="1" s="50">
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Aparte del texto hacen falta FOTOS: las de Elizabeth, Gabriela y Tonathiu (cuadradas, mín. 400×400 px). Y si existen, los enlaces de Instagram, Facebook, TikTok y WhatsApp en la pestaña «ajustes» — son opcionales, pero mientras estén vacíos esos botones no aparecen en la web.</t>
+          <t>Aparte del texto hacen falta FOTOS: las de Elizabeth, Gabriela y Tonatiuh (cuadradas, mín. 400×400 px). Y si existen, los enlaces de Instagram, Facebook, TikTok y WhatsApp en la pestaña «ajustes» — son opcionales, pero mientras estén vacíos esos botones no aparecen en la web.</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4345,7 @@
       </c>
       <c r="B12" s="45" t="inlineStr">
         <is>
-          <t>Tonathiu Muñoz</t>
+          <t>Tonatiuh Muñoz</t>
         </is>
       </c>
       <c r="C12" s="36" t="inlineStr">
@@ -4362,7 +4367,7 @@
       </c>
       <c r="C13" s="36" t="inlineStr">
         <is>
-          <t>Faltan las de Elizabeth, Gabriela y Tonathiu. Cuadradas, mínimo 400×400 px.</t>
+          <t>Faltan las de Elizabeth, Gabriela y Tonatiuh. Cuadradas, mínimo 400×400 px.</t>
         </is>
       </c>
     </row>
@@ -5716,12 +5721,12 @@
     <row r="6" ht="107.25" customHeight="1" s="50">
       <c r="A6" s="29" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="B6" s="32" t="inlineStr">
         <is>
-          <t>Tonathiu Muñoz</t>
+          <t>Tonatiuh Muñoz</t>
         </is>
       </c>
       <c r="C6" s="32" t="inlineStr">
@@ -5731,13 +5736,13 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Tonathiu se define como un ser en constante búsqueda de respuestas, crecimiento y sanación. A lo largo de su camino ha encontrado diversas técnicas, herramientas y conocimientos que le han ayudado a comprenderse mejor y a transformar aspectos importantes de su vida.
+          <t>Tonatiuh se define como un ser en constante búsqueda de respuestas, crecimiento y sanación. A lo largo de su camino ha encontrado diversas técnicas, herramientas y conocimientos que le han ayudado a comprenderse mejor y a transformar aspectos importantes de su vida.
 Hoy comparte estas experiencias y aprendizajes con el propósito de acompañar a otras personas en sus propios procesos, ofreciendo un espacio de escucha, equilibrio y reconexión con sí mismas. Su intención es apoyar a quienes buscan bienestar, claridad y una relación más profunda con su esencia.</t>
         </is>
       </c>
       <c r="E6" s="21" t="inlineStr">
         <is>
-          <t>tonathiu-munoz.jpg</t>
+          <t>tonatiuh-munoz.jpg</t>
         </is>
       </c>
       <c r="F6" s="29" t="n">
@@ -8571,7 +8576,7 @@
       </c>
       <c r="L7" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M7" s="32" t="inlineStr">
@@ -8640,7 +8645,7 @@
       </c>
       <c r="L8" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M8" s="32" t="inlineStr">
@@ -8710,7 +8715,7 @@
       </c>
       <c r="L9" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M9" s="32" t="inlineStr">
@@ -8779,7 +8784,7 @@
       </c>
       <c r="L10" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M10" s="32" t="inlineStr">
@@ -8848,7 +8853,7 @@
       </c>
       <c r="L11" s="32" t="inlineStr">
         <is>
-          <t>tonathiu-munoz</t>
+          <t>tonatiuh-munoz</t>
         </is>
       </c>
       <c r="M11" s="32" t="inlineStr">
